--- a/02_PCB/07_RBE-PWR-HOTSWAP/05_PCBA加工要求_HOTSWAP.xlsx
+++ b/02_PCB/07_RBE-PWR-HOTSWAP/05_PCBA加工要求_HOTSWAP.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="基本信息" sheetId="2" r:id="rId5"/>
-    <sheet name="附图1" sheetId="3" r:id="rId6"/>
-    <sheet name="附图2" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcMode="auto"/>
   <extLst>
@@ -49,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -172,7 +170,7 @@
     <t xml:space="preserve">说明：</t>
   </si>
   <si>
-    <t xml:space="preserve">详见附图1</t>
+    <t xml:space="preserve">无</t>
   </si>
   <si>
     <t xml:space="preserve">相关标准</t>
@@ -197,22 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">不固定自行贴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP层100Ω
-差分阻抗匹配</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOT层100Ω
-差分阻抗匹配</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOT层90Ω
-差分阻抗匹配</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIG03层120Ω
-差分阻抗匹配</t>
   </si>
 </sst>
 </file>
@@ -463,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -500,21 +482,18 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -541,15 +520,6 @@
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,155 +536,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="PwjnIV"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="false"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="false" fPrintsWithSheet="true"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="zqSNQu"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="false"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="false" fPrintsWithSheet="true"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="WCVmPm"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="false"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="false" fPrintsWithSheet="true"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>-38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="PlMSvT"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="false"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="false" fPrintsWithSheet="true"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1020,10 +841,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="23.7272727272727"/>
     <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row customHeight="true" ht="41" r="1">
@@ -1082,13 +903,13 @@
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="9">
         <v>4</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1.6</v>
       </c>
     </row>
@@ -1096,23 +917,23 @@
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="10"/>
-      <c r="D5" s="13"/>
+      <c r="D5" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="6">
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1120,13 +941,13 @@
       <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1134,53 +955,53 @@
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="13"/>
+      <c r="D8" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="9">
       <c r="A9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="10"/>
-      <c r="D9" s="13"/>
+      <c r="D9" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="10">
       <c r="A10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="13"/>
+      <c r="D10" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="11">
       <c r="A11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="10"/>
-      <c r="D11" s="13"/>
+      <c r="D11" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="12">
       <c r="A12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1188,25 +1009,25 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="13"/>
+      <c r="D13" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="14">
       <c r="A14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1214,13 +1035,13 @@
       <c r="A15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1228,1123 +1049,1123 @@
       <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="10"/>
-      <c r="D16" s="13"/>
+      <c r="D16" s="12"/>
     </row>
     <row customHeight="true" ht="20" r="17">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="18"/>
+      <c r="D17" s="17"/>
     </row>
     <row customHeight="true" ht="32" r="18">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24"/>
     </row>
     <row r="20">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
     </row>
     <row r="26">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
     </row>
     <row r="28">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
     </row>
     <row r="31">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
     </row>
     <row r="39">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
     </row>
     <row r="40">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
     </row>
     <row r="41">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
     </row>
     <row r="42">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
     </row>
     <row r="43">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
     </row>
     <row r="44">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
     </row>
     <row r="45">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
     </row>
     <row r="46">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
     </row>
     <row r="47">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
     </row>
     <row r="48">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
     </row>
     <row r="49">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
     </row>
     <row r="50">
-      <c r="A50" s="19"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
     </row>
     <row r="51">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
     </row>
     <row r="52">
-      <c r="A52" s="19"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
     </row>
     <row r="53">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
     </row>
     <row r="54">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
     </row>
     <row r="55">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
     </row>
     <row r="56">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
     </row>
     <row r="57">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
     </row>
     <row r="58">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
     </row>
     <row r="59">
-      <c r="A59" s="19"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
     </row>
     <row r="60">
-      <c r="A60" s="19"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
     </row>
     <row r="61">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
     </row>
     <row r="62">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
     </row>
     <row r="63">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
     </row>
     <row r="64">
-      <c r="A64" s="19"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
     </row>
     <row r="65">
-      <c r="A65" s="19"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
     </row>
     <row r="66">
-      <c r="A66" s="19"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
     </row>
     <row r="67">
-      <c r="A67" s="19"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
     </row>
     <row r="68">
-      <c r="A68" s="19"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
     </row>
     <row r="69">
-      <c r="A69" s="19"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
     </row>
     <row r="70">
-      <c r="A70" s="19"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
     </row>
     <row r="71">
-      <c r="A71" s="19"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
     </row>
     <row r="72">
-      <c r="A72" s="19"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
     </row>
     <row r="73">
-      <c r="A73" s="19"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
     </row>
     <row r="74">
-      <c r="A74" s="19"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
     </row>
     <row r="75">
-      <c r="A75" s="19"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
     </row>
     <row r="76">
-      <c r="A76" s="19"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
     </row>
     <row r="77">
-      <c r="A77" s="19"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
     </row>
     <row r="78">
-      <c r="A78" s="19"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
     </row>
     <row r="79">
-      <c r="A79" s="19"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
     </row>
     <row r="80">
-      <c r="A80" s="19"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
     </row>
     <row r="81">
-      <c r="A81" s="19"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="19"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
     </row>
     <row r="82">
-      <c r="A82" s="19"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
-      <c r="D82" s="19"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
     </row>
     <row r="83">
-      <c r="A83" s="19"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
     </row>
     <row r="84">
-      <c r="A84" s="19"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
     </row>
     <row r="85">
-      <c r="A85" s="19"/>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
     </row>
     <row r="86">
-      <c r="A86" s="19"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
     </row>
     <row r="87">
-      <c r="A87" s="19"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
     </row>
     <row r="88">
-      <c r="A88" s="19"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
     </row>
     <row r="89">
-      <c r="A89" s="19"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
     </row>
     <row r="90">
-      <c r="A90" s="19"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
+      <c r="A90" s="18"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
     </row>
     <row r="91">
-      <c r="A91" s="19"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
     </row>
     <row r="92">
-      <c r="A92" s="19"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
+      <c r="A92" s="18"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
     </row>
     <row r="93">
-      <c r="A93" s="19"/>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
     </row>
     <row r="94">
-      <c r="A94" s="19"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
     </row>
     <row r="95">
-      <c r="A95" s="19"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-      <c r="D95" s="19"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
     </row>
     <row r="96">
-      <c r="A96" s="19"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-      <c r="D96" s="19"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
     </row>
     <row r="97">
-      <c r="A97" s="19"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
     </row>
     <row r="98">
-      <c r="A98" s="19"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
     </row>
     <row r="99">
-      <c r="A99" s="19"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
+      <c r="A99" s="18"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="18"/>
     </row>
     <row r="100">
-      <c r="A100" s="19"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
+      <c r="A100" s="18"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="18"/>
     </row>
     <row r="101">
-      <c r="A101" s="19"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="18"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
     </row>
     <row r="102">
-      <c r="A102" s="19"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
     </row>
     <row r="103">
-      <c r="A103" s="19"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
     </row>
     <row r="104">
-      <c r="A104" s="19"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-      <c r="D104" s="19"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="18"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
     </row>
     <row r="105">
-      <c r="A105" s="19"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="19"/>
+      <c r="A105" s="18"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="18"/>
     </row>
     <row r="106">
-      <c r="A106" s="19"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-      <c r="D106" s="19"/>
+      <c r="A106" s="18"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
     </row>
     <row r="107">
-      <c r="A107" s="19"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="19"/>
+      <c r="A107" s="18"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
     </row>
     <row r="108">
-      <c r="A108" s="19"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="D108" s="19"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
     </row>
     <row r="109">
-      <c r="A109" s="19"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="D109" s="19"/>
+      <c r="A109" s="18"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
     </row>
     <row r="110">
-      <c r="A110" s="19"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="19"/>
+      <c r="A110" s="18"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
     </row>
     <row r="111">
-      <c r="A111" s="19"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
+      <c r="A111" s="18"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
     </row>
     <row r="112">
-      <c r="A112" s="19"/>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
+      <c r="A112" s="18"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
     </row>
     <row r="113">
-      <c r="A113" s="19"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-      <c r="D113" s="19"/>
+      <c r="A113" s="18"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
     </row>
     <row r="114">
-      <c r="A114" s="19"/>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-      <c r="D114" s="19"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
     </row>
     <row r="115">
-      <c r="A115" s="19"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
+      <c r="A115" s="18"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
     </row>
     <row r="116">
-      <c r="A116" s="19"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-      <c r="D116" s="19"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
     </row>
     <row r="117">
-      <c r="A117" s="19"/>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-      <c r="D117" s="19"/>
+      <c r="A117" s="18"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
     </row>
     <row r="118">
-      <c r="A118" s="19"/>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="19"/>
+      <c r="A118" s="18"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="18"/>
     </row>
     <row r="119">
-      <c r="A119" s="19"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-      <c r="D119" s="19"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
     </row>
     <row r="120">
-      <c r="A120" s="19"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-      <c r="D120" s="19"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="18"/>
     </row>
     <row r="121">
-      <c r="A121" s="19"/>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="19"/>
+      <c r="A121" s="18"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
     </row>
     <row r="122">
-      <c r="A122" s="19"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-      <c r="D122" s="19"/>
+      <c r="A122" s="18"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
     </row>
     <row r="123">
-      <c r="A123" s="19"/>
-      <c r="B123" s="19"/>
-      <c r="C123" s="19"/>
-      <c r="D123" s="19"/>
+      <c r="A123" s="18"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
     </row>
     <row r="124">
-      <c r="A124" s="19"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
-      <c r="D124" s="19"/>
+      <c r="A124" s="18"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
     </row>
     <row r="125">
-      <c r="A125" s="19"/>
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-      <c r="D125" s="19"/>
+      <c r="A125" s="18"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="18"/>
     </row>
     <row r="126">
-      <c r="A126" s="19"/>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="19"/>
+      <c r="A126" s="18"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="18"/>
     </row>
     <row r="127">
-      <c r="A127" s="19"/>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="19"/>
+      <c r="A127" s="18"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="18"/>
     </row>
     <row r="128">
-      <c r="A128" s="19"/>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
+      <c r="A128" s="18"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
     </row>
     <row r="129">
-      <c r="A129" s="19"/>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="19"/>
+      <c r="A129" s="18"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
     </row>
     <row r="130">
-      <c r="A130" s="19"/>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="19"/>
+      <c r="A130" s="18"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
     </row>
     <row r="131">
-      <c r="A131" s="19"/>
-      <c r="B131" s="19"/>
-      <c r="C131" s="19"/>
-      <c r="D131" s="19"/>
+      <c r="A131" s="18"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
     </row>
     <row r="132">
-      <c r="A132" s="19"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="19"/>
-      <c r="D132" s="19"/>
+      <c r="A132" s="18"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
     </row>
     <row r="133">
-      <c r="A133" s="19"/>
-      <c r="B133" s="19"/>
-      <c r="C133" s="19"/>
-      <c r="D133" s="19"/>
+      <c r="A133" s="18"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
     </row>
     <row r="134">
-      <c r="A134" s="19"/>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-      <c r="D134" s="19"/>
+      <c r="A134" s="18"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
     </row>
     <row r="135">
-      <c r="A135" s="19"/>
-      <c r="B135" s="19"/>
-      <c r="C135" s="19"/>
-      <c r="D135" s="19"/>
+      <c r="A135" s="18"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
     </row>
     <row r="136">
-      <c r="A136" s="19"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
-      <c r="D136" s="19"/>
+      <c r="A136" s="18"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
     </row>
     <row r="137">
-      <c r="A137" s="19"/>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-      <c r="D137" s="19"/>
+      <c r="A137" s="18"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
     </row>
     <row r="138">
-      <c r="A138" s="19"/>
-      <c r="B138" s="19"/>
-      <c r="C138" s="19"/>
-      <c r="D138" s="19"/>
+      <c r="A138" s="18"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
     </row>
     <row r="139">
-      <c r="A139" s="19"/>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
-      <c r="D139" s="19"/>
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
     </row>
     <row r="140">
-      <c r="A140" s="19"/>
-      <c r="B140" s="19"/>
-      <c r="C140" s="19"/>
-      <c r="D140" s="19"/>
+      <c r="A140" s="18"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
     </row>
     <row r="141">
-      <c r="A141" s="19"/>
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-      <c r="D141" s="19"/>
+      <c r="A141" s="18"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
     </row>
     <row r="142">
-      <c r="A142" s="19"/>
-      <c r="B142" s="19"/>
-      <c r="C142" s="19"/>
-      <c r="D142" s="19"/>
+      <c r="A142" s="18"/>
+      <c r="B142" s="18"/>
+      <c r="C142" s="18"/>
+      <c r="D142" s="18"/>
     </row>
     <row r="143">
-      <c r="A143" s="19"/>
-      <c r="B143" s="19"/>
-      <c r="C143" s="19"/>
-      <c r="D143" s="19"/>
+      <c r="A143" s="18"/>
+      <c r="B143" s="18"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
     </row>
     <row r="144">
-      <c r="A144" s="19"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
-      <c r="D144" s="19"/>
+      <c r="A144" s="18"/>
+      <c r="B144" s="18"/>
+      <c r="C144" s="18"/>
+      <c r="D144" s="18"/>
     </row>
     <row r="145">
-      <c r="A145" s="19"/>
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
-      <c r="D145" s="19"/>
+      <c r="A145" s="18"/>
+      <c r="B145" s="18"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="18"/>
     </row>
     <row r="146">
-      <c r="A146" s="19"/>
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
-      <c r="D146" s="19"/>
+      <c r="A146" s="18"/>
+      <c r="B146" s="18"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="18"/>
     </row>
     <row r="147">
-      <c r="A147" s="19"/>
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-      <c r="D147" s="19"/>
+      <c r="A147" s="18"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18"/>
+      <c r="D147" s="18"/>
     </row>
     <row r="148">
-      <c r="A148" s="19"/>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-      <c r="D148" s="19"/>
+      <c r="A148" s="18"/>
+      <c r="B148" s="18"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="18"/>
     </row>
     <row r="149">
-      <c r="A149" s="19"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="19"/>
+      <c r="A149" s="18"/>
+      <c r="B149" s="18"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
     </row>
     <row r="150">
-      <c r="A150" s="19"/>
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-      <c r="D150" s="19"/>
+      <c r="A150" s="18"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
     </row>
     <row r="151">
-      <c r="A151" s="19"/>
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-      <c r="D151" s="19"/>
+      <c r="A151" s="18"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
     </row>
     <row r="152">
-      <c r="A152" s="19"/>
-      <c r="B152" s="19"/>
-      <c r="C152" s="19"/>
-      <c r="D152" s="19"/>
+      <c r="A152" s="18"/>
+      <c r="B152" s="18"/>
+      <c r="C152" s="18"/>
+      <c r="D152" s="18"/>
     </row>
     <row r="153">
-      <c r="A153" s="19"/>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
-      <c r="D153" s="19"/>
+      <c r="A153" s="18"/>
+      <c r="B153" s="18"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="18"/>
     </row>
     <row r="154">
-      <c r="A154" s="19"/>
-      <c r="B154" s="19"/>
-      <c r="C154" s="19"/>
-      <c r="D154" s="19"/>
+      <c r="A154" s="18"/>
+      <c r="B154" s="18"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="18"/>
     </row>
     <row r="155">
-      <c r="A155" s="19"/>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-      <c r="D155" s="19"/>
+      <c r="A155" s="18"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="18"/>
     </row>
     <row r="156">
-      <c r="A156" s="19"/>
-      <c r="B156" s="19"/>
-      <c r="C156" s="19"/>
-      <c r="D156" s="19"/>
+      <c r="A156" s="18"/>
+      <c r="B156" s="18"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="18"/>
     </row>
     <row r="157">
-      <c r="A157" s="19"/>
-      <c r="B157" s="19"/>
-      <c r="C157" s="19"/>
-      <c r="D157" s="19"/>
+      <c r="A157" s="18"/>
+      <c r="B157" s="18"/>
+      <c r="C157" s="18"/>
+      <c r="D157" s="18"/>
     </row>
     <row r="158">
-      <c r="A158" s="19"/>
-      <c r="B158" s="19"/>
-      <c r="C158" s="19"/>
-      <c r="D158" s="19"/>
+      <c r="A158" s="18"/>
+      <c r="B158" s="18"/>
+      <c r="C158" s="18"/>
+      <c r="D158" s="18"/>
     </row>
     <row r="159">
-      <c r="A159" s="19"/>
-      <c r="B159" s="19"/>
-      <c r="C159" s="19"/>
-      <c r="D159" s="19"/>
+      <c r="A159" s="18"/>
+      <c r="B159" s="18"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="18"/>
     </row>
     <row r="160">
-      <c r="A160" s="19"/>
-      <c r="B160" s="19"/>
-      <c r="C160" s="19"/>
-      <c r="D160" s="19"/>
+      <c r="A160" s="18"/>
+      <c r="B160" s="18"/>
+      <c r="C160" s="18"/>
+      <c r="D160" s="18"/>
     </row>
     <row r="161">
-      <c r="A161" s="19"/>
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
-      <c r="D161" s="19"/>
+      <c r="A161" s="18"/>
+      <c r="B161" s="18"/>
+      <c r="C161" s="18"/>
+      <c r="D161" s="18"/>
     </row>
     <row r="162">
-      <c r="A162" s="19"/>
-      <c r="B162" s="19"/>
-      <c r="C162" s="19"/>
-      <c r="D162" s="19"/>
+      <c r="A162" s="18"/>
+      <c r="B162" s="18"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="18"/>
     </row>
     <row r="163">
-      <c r="A163" s="19"/>
-      <c r="B163" s="19"/>
-      <c r="C163" s="19"/>
-      <c r="D163" s="19"/>
+      <c r="A163" s="18"/>
+      <c r="B163" s="18"/>
+      <c r="C163" s="18"/>
+      <c r="D163" s="18"/>
     </row>
     <row r="164">
-      <c r="A164" s="19"/>
-      <c r="B164" s="19"/>
-      <c r="C164" s="19"/>
-      <c r="D164" s="19"/>
+      <c r="A164" s="18"/>
+      <c r="B164" s="18"/>
+      <c r="C164" s="18"/>
+      <c r="D164" s="18"/>
     </row>
     <row r="165">
-      <c r="A165" s="19"/>
-      <c r="B165" s="19"/>
-      <c r="C165" s="19"/>
-      <c r="D165" s="19"/>
+      <c r="A165" s="18"/>
+      <c r="B165" s="18"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="18"/>
     </row>
     <row r="166">
-      <c r="A166" s="19"/>
-      <c r="B166" s="19"/>
-      <c r="C166" s="19"/>
-      <c r="D166" s="19"/>
+      <c r="A166" s="18"/>
+      <c r="B166" s="18"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="18"/>
     </row>
     <row r="167">
-      <c r="A167" s="19"/>
-      <c r="B167" s="19"/>
-      <c r="C167" s="19"/>
-      <c r="D167" s="19"/>
+      <c r="A167" s="18"/>
+      <c r="B167" s="18"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
     </row>
     <row r="168">
-      <c r="A168" s="19"/>
-      <c r="B168" s="19"/>
-      <c r="C168" s="19"/>
-      <c r="D168" s="19"/>
+      <c r="A168" s="18"/>
+      <c r="B168" s="18"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
     </row>
     <row r="169">
-      <c r="A169" s="19"/>
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
-      <c r="D169" s="19"/>
+      <c r="A169" s="18"/>
+      <c r="B169" s="18"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="18"/>
     </row>
     <row r="170">
-      <c r="A170" s="19"/>
-      <c r="B170" s="19"/>
-      <c r="C170" s="19"/>
-      <c r="D170" s="19"/>
+      <c r="A170" s="18"/>
+      <c r="B170" s="18"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="18"/>
     </row>
     <row r="171">
-      <c r="A171" s="19"/>
-      <c r="B171" s="19"/>
-      <c r="C171" s="19"/>
-      <c r="D171" s="19"/>
+      <c r="A171" s="18"/>
+      <c r="B171" s="18"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="18"/>
     </row>
     <row r="172">
-      <c r="A172" s="19"/>
-      <c r="B172" s="19"/>
-      <c r="C172" s="19"/>
-      <c r="D172" s="19"/>
+      <c r="A172" s="18"/>
+      <c r="B172" s="18"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="18"/>
     </row>
     <row r="173">
-      <c r="A173" s="19"/>
-      <c r="B173" s="19"/>
-      <c r="C173" s="19"/>
-      <c r="D173" s="19"/>
+      <c r="A173" s="18"/>
+      <c r="B173" s="18"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="18"/>
     </row>
     <row r="174">
-      <c r="A174" s="19"/>
-      <c r="B174" s="19"/>
-      <c r="C174" s="19"/>
-      <c r="D174" s="19"/>
+      <c r="A174" s="18"/>
+      <c r="B174" s="18"/>
+      <c r="C174" s="18"/>
+      <c r="D174" s="18"/>
     </row>
     <row r="175">
-      <c r="A175" s="19"/>
-      <c r="B175" s="19"/>
-      <c r="C175" s="19"/>
-      <c r="D175" s="19"/>
+      <c r="A175" s="18"/>
+      <c r="B175" s="18"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="18"/>
     </row>
     <row r="176">
-      <c r="A176" s="19"/>
-      <c r="B176" s="19"/>
-      <c r="C176" s="19"/>
-      <c r="D176" s="19"/>
+      <c r="A176" s="18"/>
+      <c r="B176" s="18"/>
+      <c r="C176" s="18"/>
+      <c r="D176" s="18"/>
     </row>
     <row r="177">
-      <c r="A177" s="19"/>
-      <c r="B177" s="19"/>
-      <c r="C177" s="19"/>
-      <c r="D177" s="19"/>
+      <c r="A177" s="18"/>
+      <c r="B177" s="18"/>
+      <c r="C177" s="18"/>
+      <c r="D177" s="18"/>
     </row>
     <row r="178">
-      <c r="A178" s="19"/>
-      <c r="B178" s="19"/>
-      <c r="C178" s="19"/>
-      <c r="D178" s="19"/>
+      <c r="A178" s="18"/>
+      <c r="B178" s="18"/>
+      <c r="C178" s="18"/>
+      <c r="D178" s="18"/>
     </row>
     <row r="179">
-      <c r="A179" s="19"/>
-      <c r="B179" s="19"/>
-      <c r="C179" s="19"/>
-      <c r="D179" s="19"/>
+      <c r="A179" s="18"/>
+      <c r="B179" s="18"/>
+      <c r="C179" s="18"/>
+      <c r="D179" s="18"/>
     </row>
     <row r="180">
-      <c r="A180" s="19"/>
-      <c r="B180" s="19"/>
-      <c r="C180" s="19"/>
-      <c r="D180" s="19"/>
+      <c r="A180" s="18"/>
+      <c r="B180" s="18"/>
+      <c r="C180" s="18"/>
+      <c r="D180" s="18"/>
     </row>
     <row r="181">
-      <c r="A181" s="19"/>
-      <c r="B181" s="19"/>
-      <c r="C181" s="19"/>
-      <c r="D181" s="19"/>
+      <c r="A181" s="18"/>
+      <c r="B181" s="18"/>
+      <c r="C181" s="18"/>
+      <c r="D181" s="18"/>
     </row>
     <row r="182">
-      <c r="A182" s="19"/>
-      <c r="B182" s="19"/>
-      <c r="C182" s="19"/>
-      <c r="D182" s="19"/>
+      <c r="A182" s="18"/>
+      <c r="B182" s="18"/>
+      <c r="C182" s="18"/>
+      <c r="D182" s="18"/>
     </row>
     <row r="183">
-      <c r="A183" s="19"/>
-      <c r="B183" s="19"/>
-      <c r="C183" s="19"/>
-      <c r="D183" s="19"/>
+      <c r="A183" s="18"/>
+      <c r="B183" s="18"/>
+      <c r="C183" s="18"/>
+      <c r="D183" s="18"/>
     </row>
     <row r="184">
-      <c r="A184" s="19"/>
-      <c r="B184" s="19"/>
-      <c r="C184" s="19"/>
-      <c r="D184" s="19"/>
+      <c r="A184" s="18"/>
+      <c r="B184" s="18"/>
+      <c r="C184" s="18"/>
+      <c r="D184" s="18"/>
     </row>
     <row r="185">
-      <c r="A185" s="19"/>
-      <c r="B185" s="19"/>
-      <c r="C185" s="19"/>
-      <c r="D185" s="19"/>
+      <c r="A185" s="18"/>
+      <c r="B185" s="18"/>
+      <c r="C185" s="18"/>
+      <c r="D185" s="18"/>
     </row>
     <row r="186">
-      <c r="A186" s="19"/>
-      <c r="B186" s="19"/>
-      <c r="C186" s="19"/>
-      <c r="D186" s="19"/>
+      <c r="A186" s="18"/>
+      <c r="B186" s="18"/>
+      <c r="C186" s="18"/>
+      <c r="D186" s="18"/>
     </row>
     <row r="187">
-      <c r="A187" s="19"/>
-      <c r="B187" s="19"/>
-      <c r="C187" s="19"/>
-      <c r="D187" s="19"/>
+      <c r="A187" s="18"/>
+      <c r="B187" s="18"/>
+      <c r="C187" s="18"/>
+      <c r="D187" s="18"/>
     </row>
     <row r="188">
-      <c r="A188" s="19"/>
-      <c r="B188" s="19"/>
-      <c r="C188" s="19"/>
-      <c r="D188" s="19"/>
+      <c r="A188" s="18"/>
+      <c r="B188" s="18"/>
+      <c r="C188" s="18"/>
+      <c r="D188" s="18"/>
     </row>
     <row r="189">
-      <c r="A189" s="19"/>
-      <c r="B189" s="19"/>
-      <c r="C189" s="19"/>
-      <c r="D189" s="19"/>
+      <c r="A189" s="18"/>
+      <c r="B189" s="18"/>
+      <c r="C189" s="18"/>
+      <c r="D189" s="18"/>
     </row>
     <row r="190">
-      <c r="A190" s="19"/>
-      <c r="B190" s="19"/>
-      <c r="C190" s="19"/>
-      <c r="D190" s="19"/>
+      <c r="A190" s="18"/>
+      <c r="B190" s="18"/>
+      <c r="C190" s="18"/>
+      <c r="D190" s="18"/>
     </row>
     <row r="191">
-      <c r="A191" s="19"/>
-      <c r="B191" s="19"/>
-      <c r="C191" s="19"/>
-      <c r="D191" s="19"/>
+      <c r="A191" s="18"/>
+      <c r="B191" s="18"/>
+      <c r="C191" s="18"/>
+      <c r="D191" s="18"/>
     </row>
     <row r="192">
-      <c r="A192" s="19"/>
-      <c r="B192" s="19"/>
-      <c r="C192" s="19"/>
-      <c r="D192" s="19"/>
+      <c r="A192" s="18"/>
+      <c r="B192" s="18"/>
+      <c r="C192" s="18"/>
+      <c r="D192" s="18"/>
     </row>
     <row r="193">
-      <c r="A193" s="19"/>
-      <c r="B193" s="19"/>
-      <c r="C193" s="19"/>
-      <c r="D193" s="19"/>
+      <c r="A193" s="18"/>
+      <c r="B193" s="18"/>
+      <c r="C193" s="18"/>
+      <c r="D193" s="18"/>
     </row>
     <row r="194">
-      <c r="A194" s="19"/>
-      <c r="B194" s="19"/>
-      <c r="C194" s="19"/>
-      <c r="D194" s="19"/>
+      <c r="A194" s="18"/>
+      <c r="B194" s="18"/>
+      <c r="C194" s="18"/>
+      <c r="D194" s="18"/>
     </row>
     <row r="195">
-      <c r="A195" s="19"/>
-      <c r="B195" s="19"/>
-      <c r="C195" s="19"/>
-      <c r="D195" s="19"/>
+      <c r="A195" s="18"/>
+      <c r="B195" s="18"/>
+      <c r="C195" s="18"/>
+      <c r="D195" s="18"/>
     </row>
     <row r="196">
-      <c r="A196" s="19"/>
-      <c r="B196" s="19"/>
-      <c r="C196" s="19"/>
-      <c r="D196" s="19"/>
+      <c r="A196" s="18"/>
+      <c r="B196" s="18"/>
+      <c r="C196" s="18"/>
+      <c r="D196" s="18"/>
     </row>
     <row r="197">
-      <c r="A197" s="19"/>
-      <c r="B197" s="19"/>
-      <c r="C197" s="19"/>
-      <c r="D197" s="19"/>
+      <c r="A197" s="18"/>
+      <c r="B197" s="18"/>
+      <c r="C197" s="18"/>
+      <c r="D197" s="18"/>
     </row>
     <row r="198">
-      <c r="A198" s="19"/>
-      <c r="B198" s="19"/>
-      <c r="C198" s="19"/>
-      <c r="D198" s="19"/>
+      <c r="A198" s="18"/>
+      <c r="B198" s="18"/>
+      <c r="C198" s="18"/>
+      <c r="D198" s="18"/>
     </row>
     <row r="199">
-      <c r="A199" s="19"/>
-      <c r="B199" s="19"/>
-      <c r="C199" s="19"/>
-      <c r="D199" s="19"/>
+      <c r="A199" s="18"/>
+      <c r="B199" s="18"/>
+      <c r="C199" s="18"/>
+      <c r="D199" s="18"/>
     </row>
     <row r="200">
-      <c r="A200" s="19"/>
-      <c r="B200" s="19"/>
-      <c r="C200" s="19"/>
-      <c r="D200" s="19"/>
+      <c r="A200" s="18"/>
+      <c r="B200" s="18"/>
+      <c r="C200" s="18"/>
+      <c r="D200" s="18"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -2353,20 +2174,38 @@
     <mergeCell ref="B18:D19"/>
   </mergeCells>
   <dataValidations count="15">
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B4:B4" type="list">
-      <formula1>"2,4,6,8,10,12"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B8:B8" type="list">
-      <formula1>"按合同数量,自定义"</formula1>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="D12:D12" type="list">
       <formula1>"0.5OZ,1OZ,2OZ"</formula1>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B16:B16" type="list">
       <formula1>"不拼板,供应商自行拼板,自定义"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="D4:D4" type="list">
-      <formula1>"0.8,1.0,1.2,1.6,2.0"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B4:B4" type="list">
+      <formula1>"2,4,6,8,10,12"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="D7:D7" type="list">
+      <formula1>"白色,黑色"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B15:B15" type="list">
+      <formula1>"ROHS,REACH"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B11:B11" type="list">
+      <formula1>"盖油,塞油,树脂塞孔,灌铜"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B12:B12" type="list">
+      <formula1>"1OZ,2OZ,3OZ"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B14:B14" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B7:B7" type="list">
+      <formula1>"绿色,蓝色,黑色,红色,白色"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B9:B9" type="list">
+      <formula1>"按GERBER,按PCB文件"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B8:B8" type="list">
+      <formula1>"按合同数量,自定义"</formula1>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B13:B13" type="list">
       <formula1>"二级"</formula1>
@@ -2374,99 +2213,15 @@
     <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B17:B17" type="list">
       <formula1>"不固定自行贴,固定Label区域"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="D4:D4" type="list">
+      <formula1>"0.8,1.0,1.2,1.6,2.0"</formula1>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B6:B6" type="list">
       <formula1>"FR-4,铝基板,铜基板,陶瓷板,高TG板材"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B9:B9" type="list">
-      <formula1>"按GERBER,按PCB文件"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B14:B14" type="list">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B7:B7" type="list">
-      <formula1>"绿色,蓝色,黑色,红色,白色"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="D7:D7" type="list">
-      <formula1>"白色,黑色"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B11:B11" type="list">
-      <formula1>"盖油,塞油,树脂塞孔,灌铜"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B12:B12" type="list">
-      <formula1>"1OZ,2OZ,3OZ"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B15:B15" type="list">
-      <formula1>"ROHS,REACH"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100"/>
   <picture r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="60.0909090909091"/>
-  </cols>
-  <sheetData>
-    <row customHeight="true" ht="360" r="1">
-      <c r="A1" s="26"/>
-      <c r="B1" s="27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row customHeight="true" ht="365" r="2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
-  <drawing r:id="rId1"/>
-  <picture r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="54.9090909090909"/>
-  </cols>
-  <sheetData>
-    <row customHeight="true" ht="230" r="1"/>
-    <row customHeight="true" ht="53" r="2">
-      <c r="A2" s="28"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
-  <picture r:id="rId1"/>
-</worksheet>
 </file>